--- a/tools/importer/reports/import-chevron-homepage.report.xlsx
+++ b/tools/importer/reports/import-chevron-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="620">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>contact-us.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","cards-service","cards-service","cards-service"]</t>
+  </si>
+  <si>
+    <t>contact-us</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>expertise-where-to-buy</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:56:12.608Z</t>
+  </si>
+  <si>
+    <t>Contact Us | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/contact-us.html</t>
+  </si>
+  <si>
     <t>home.report.json</t>
   </si>
   <si>
@@ -46,13 +70,10 @@
     <t>home</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>chevron-homepage</t>
   </si>
   <si>
-    <t>2026-10-29T00:31:55.364Z</t>
+    <t>2026-10-30T02:59:14.535Z</t>
   </si>
   <si>
     <t>Premium Lubricants and Coolants | Chevron Lubricants (US)</t>
@@ -68,6 +89,1788 @@
   </si>
   <si>
     <t>2026-10-29T00:16:52.205Z</t>
+  </si>
+  <si>
+    <t>en-us/home.report.json</t>
+  </si>
+  <si>
+    <t>en-us/home</t>
+  </si>
+  <si>
+    <t>2026-10-30T14:07:44.958Z</t>
+  </si>
+  <si>
+    <t>where-to-buy/find-a-distributor.report.json</t>
+  </si>
+  <si>
+    <t>["locator"]</t>
+  </si>
+  <si>
+    <t>where-to-buy/find-a-distributor</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:55:49.144Z</t>
+  </si>
+  <si>
+    <t>Find a Distributor | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/where-to-buy/find-a-distributor.html</t>
+  </si>
+  <si>
+    <t>where-to-buy/find-a-retailer.report.json</t>
+  </si>
+  <si>
+    <t>where-to-buy/find-a-retailer</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:56:03.959Z</t>
+  </si>
+  <si>
+    <t>Find a retailer | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/where-to-buy/find-a-retailer.html</t>
+  </si>
+  <si>
+    <t>where-to-buy/find-an-installer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-overlay","columns-cta","cards-resource","locator"]</t>
+  </si>
+  <si>
+    <t>where-to-buy/find-an-installer</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:55:55.487Z</t>
+  </si>
+  <si>
+    <t>Find Oil Change Locations Near Me | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/where-to-buy/find-an-installer.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","quote-testimonial","columns-cta","cards-service","cards-service"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo</t>
+  </si>
+  <si>
+    <t>expertise-marketing</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:00:12.840Z</t>
+  </si>
+  <si>
+    <t>Delo Heavy Duty Engine Oils, Coolants, Lubes &amp; Greases | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:44:33.356Z</t>
+  </si>
+  <si>
+    <t>Havoline Conventional &amp; Synthetic Motor Oils | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/havoline.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products.report.json</t>
+  </si>
+  <si>
+    <t>["cards-service","cards-service"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:01:42.506Z</t>
+  </si>
+  <si>
+    <t>Industrial Lubricants - Chevron Lubricants | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-banner","accordion-drawer","accordion-drawer","accordion-drawer","quote-testimonial","hero-callout","columns-cta","cards-resource","cards-resource","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:22:08.485Z</t>
+  </si>
+  <si>
+    <t>ISOCLEAN Certified Lubricants - Chevron Lubricants | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/techron.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-square","hero-overlay","columns-cta","cards-service","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/techron</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:44:24.370Z</t>
+  </si>
+  <si>
+    <t>Techron Fuel System Cleaners &amp; Fuel Additives | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/techron.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/xpress-lube.report.json</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/xpress-lube</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:57:30.141Z</t>
+  </si>
+  <si>
+    <t>Xpress Lube | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/xpress-lube.html</t>
+  </si>
+  <si>
+    <t>learning/from-chevron/chevron-lubematters-blog-landing.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","columns-media","cards-insights","cards-insights","cards-insights"]</t>
+  </si>
+  <si>
+    <t>learning/from-chevron/chevron-lubematters-blog-landing</t>
+  </si>
+  <si>
+    <t>expertise-blog-landing</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:45:16.082Z</t>
+  </si>
+  <si>
+    <t>Chevron Lube Matters | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/from-chevron/chevron-lubematters-blog-landing.html</t>
+  </si>
+  <si>
+    <t>products/by-brand/delo.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/by-brand/delo</t>
+  </si>
+  <si>
+    <t>products-brand</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:59:22.850Z</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/by_brand/delo.html</t>
+  </si>
+  <si>
+    <t>products/by-brand/havoline.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/by-brand/havoline</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:15:45.672Z</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/by_brand/havoline.html</t>
+  </si>
+  <si>
+    <t>products/by-brand/industrial-products.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/by-brand/industrial-products</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:59:41.103Z</t>
+  </si>
+  <si>
+    <t>Industrial Lubricants | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/by_brand/industrial_products.html</t>
+  </si>
+  <si>
+    <t>products/by-brand/isoclean.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/by-brand/isoclean</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:59:49.037Z</t>
+  </si>
+  <si>
+    <t>ISOCLEAN Info Center | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/by_brand/isoclean.html</t>
+  </si>
+  <si>
+    <t>products/by-brand/techron.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products"]</t>
+  </si>
+  <si>
+    <t>products/by-brand/techron</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:59:55.001Z</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/by_brand/techron.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/coolant-landing-page.report.json</t>
+  </si>
+  <si>
+    <t>["hero-overlay","cards-service","columns-media","columns-media","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/coolant-landing-page</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:22:45.350Z</t>
+  </si>
+  <si>
+    <t>Coolant Landing Page | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo/coolant-landing-page.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/delo-customer-success-stories.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-square","columns-cta","cards-resource","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/delo-customer-success-stories</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:00:28.982Z</t>
+  </si>
+  <si>
+    <t>Delo Customer Success Stories | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo/delo-customer-success-stories.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/simplify-your-fleet-protection.report.json</t>
+  </si>
+  <si>
+    <t>["cards-service","cards-resource","cards-resource","cards-resource","cards-resource","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/simplify-your-fleet-protection</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:22:31.336Z</t>
+  </si>
+  <si>
+    <t>Simplify your fleet protection | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo/simplify-your-fleet-protection.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/the-delo-difference.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/the-delo-difference</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:00:50.106Z</t>
+  </si>
+  <si>
+    <t>The Delo Difference | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo/the-delo-difference.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/tractor-restoration-competition.report.json</t>
+  </si>
+  <si>
+    <t>["cards-resource","cards-resource","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/tractor-restoration-competition</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:22:38.360Z</t>
+  </si>
+  <si>
+    <t>Tractor Restoration Competition | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo/tractor-restoration-competition.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/business.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/business</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:58:00.056Z</t>
+  </si>
+  <si>
+    <t>Business | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/havoline/business.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/drivers.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/drivers</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:44:40.566Z</t>
+  </si>
+  <si>
+    <t>Drivers | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/havoline/drivers.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/gf-7-landing-page.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq","hero-overlay","columns-cta","columns-promo","cards-service","cards-service"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/gf-7-landing-page</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:44:16.677Z</t>
+  </si>
+  <si>
+    <t>Havoline GF-7 Motor Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/havoline/gf-7-landing-page.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/havoline-customer-stories.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","cards-resource","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/havoline/havoline-customer-stories</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:44:47.783Z</t>
+  </si>
+  <si>
+    <t>Havoline Customer Stories | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/havoline/havoline-customer-stories.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/choosing-industrial-engine-oil.report.json</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/choosing-industrial-engine-oil</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:01:50.611Z</t>
+  </si>
+  <si>
+    <t>Choosing Industrial Engine Oil | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/choosing-industrial-engine-oil.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/clarity-landing-page.report.json</t>
+  </si>
+  <si>
+    <t>["cards-resource","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/clarity-landing-page</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:22:24.156Z</t>
+  </si>
+  <si>
+    <t>Clarity Landing Page | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/clarity-landing-page.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/greaseportfolio.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","columns-cta"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/greaseportfolio</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:02:04.875Z</t>
+  </si>
+  <si>
+    <t>Grease Portfolio | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/greaseportfolio.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/how-hydraulic-oils-impact-efficiency.report.json</t>
+  </si>
+  <si>
+    <t>["cards-service","cards-service","cards-resource","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/how-hydraulic-oils-impact-efficiency</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:16:33.903Z</t>
+  </si>
+  <si>
+    <t>How Hydraulic Oils Impact Efficiency | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/how-hydraulic-oils-impact-efficiency.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/industrial-products-faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/industrial-products-faqs</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:23:43.902Z</t>
+  </si>
+  <si>
+    <t>Industrial Products FAQs | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/industrial-products-faqs.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/learning-for-you.report.json</t>
+  </si>
+  <si>
+    <t>["cards-filterable","cards-service","cards-service","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/learning-for-you</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:02:24.243Z</t>
+  </si>
+  <si>
+    <t>INDUSTRIAL Info Center | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/learning-for-you.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/vartech-isc.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-banner","columns-promo","cards-service","cards-resource","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/industrial-products/vartech-isc</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:22:16.370Z</t>
+  </si>
+  <si>
+    <t>VARTECH ISC: Clean Right. Run Right | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/industrial-products/vartech-isc.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/construction-new-oil-is-costing-you.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","cards-resource","cards-resource","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/construction-new-oil-is-costing-you</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:23:16.423Z</t>
+  </si>
+  <si>
+    <t>What is Contaminated Oil Costing You | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/construction-new-oil-is-costing-you.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/customer-success.report.json</t>
+  </si>
+  <si>
+    <t>["hero-overlay","cards-resource","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/customer-success</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:02:50.989Z</t>
+  </si>
+  <si>
+    <t>ISOCLEAN Customer Success Stories | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/customer-success.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/isoclean-faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq","columns-cta","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/isoclean-faqs</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:02:59.173Z</t>
+  </si>
+  <si>
+    <t>ISOCLEAN Certified Lubricants FAQs | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/isoclean-faqs.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/learning-for-you.report.json</t>
+  </si>
+  <si>
+    <t>["cards-filterable","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/learning-for-you</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:03:07.737Z</t>
+  </si>
+  <si>
+    <t>ISOCLEAN Info Center | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/learning-for-you.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/mining-did-you-check-the-third-spec.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-square","columns-cta","cards-resource","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/mining-did-you-check-the-third-spec</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:23:23.169Z</t>
+  </si>
+  <si>
+    <t>Do Your Mining Lubricants Meet Cleanliness Specs | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/mining-did-you-check-the-third-spec.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/oil-and-gas-svcs-the-impact-of-dirty-oil.report.json</t>
+  </si>
+  <si>
+    <t>["cards-resource","cards-resource"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/oil-and-gas-svcs-the-impact-of-dirty-oil</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:03:22.271Z</t>
+  </si>
+  <si>
+    <t>Oil and Gas SVCS - The impact of dirty oil | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/oil-and-gas-svcs-the-impact-of-dirty-oil.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/waste-hauling-does-your-new-oil-meet-the-third-spec.report.json</t>
+  </si>
+  <si>
+    <t>["columns-cta","cards-resource","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/isoclean/waste-hauling-does-your-new-oil-meet-the-third-spec</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:23:08.938Z</t>
+  </si>
+  <si>
+    <t>Waste Trucks: Is Your New Oil Clean Enough? | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/isoclean/waste-hauling-does-your-new-oil-meet-the-third-spec.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/techron/faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-cta","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/techron/faqs</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:57:44.702Z</t>
+  </si>
+  <si>
+    <t>How Techron Works &amp; How To Use Techron | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/techron/faqs.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/techron/history.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-drawer","columns-cta","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/techron/history</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:57:53.643Z</t>
+  </si>
+  <si>
+    <t>History | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/techron/history.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/xpress-lube/drivers.report.json</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/xpress-lube/drivers</t>
+  </si>
+  <si>
+    <t>2026-10-30T05:57:36.595Z</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/xpress-lube/drivers.html</t>
+  </si>
+  <si>
+    <t>learning/from-chevron/heavy-duty-diesel-vehicles-and-equipment/get-more-efficiency-from-the-workhorse-fuel.report.json</t>
+  </si>
+  <si>
+    <t>["cards-filterable"]</t>
+  </si>
+  <si>
+    <t>learning/from-chevron/heavy-duty-diesel-vehicles-and-equipment/get-more-efficiency-from-the-workhorse-fuel</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:04:10.646Z</t>
+  </si>
+  <si>
+    <t>Get More Efficiency from the “Workhorse” Fuel | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/from-chevron/heavy-duty-diesel-vehicles-and-equipment/get-more-efficiency-from-the-workhorse-fuel.html</t>
+  </si>
+  <si>
+    <t>learning/from-chevron/industrial-machinery/smaller-eservoirs-and-hotter-operating-temps-change-hydraulic-fluid-selection.report.json</t>
+  </si>
+  <si>
+    <t>learning/from-chevron/industrial-machinery/smaller-eservoirs-and-hotter-operating-temps-change-hydraulic-fluid-selection</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:04:18.802Z</t>
+  </si>
+  <si>
+    <t>Smaller Reservoirs and Hotter Operating Temps Change Hydraulic Fluid Selection | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/from-chevron/industrial-machinery/smaller-eservoirs-and-hotter-operating-temps-change-hydraulic-fluid-selection.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/gasoline-fleets-oil-change-service-centers/automobile-fleets.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/gasoline-fleets-oil-change-service-centers/automobile-fleets</t>
+  </si>
+  <si>
+    <t>products-listing</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:05:20.827Z</t>
+  </si>
+  <si>
+    <t>Products for Automobile Fleets: Lubricants, Coolants &amp; More | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/gasoline_fleets_oil_change_service_centers/automobile_fleets.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/gasoline-fleets-oil-change-service-centers/oil-change-service-centers.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/equipment-type/gasoline-fleets-oil-change-service-centers/oil-change-service-centers</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:05:27.655Z</t>
+  </si>
+  <si>
+    <t>Products for Oil Change Service Centers | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/gasoline_fleets_oil_change_service_centers/oil_change_service_centers.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/gasoline-fleets-oil-change-service-centers/truck-fleets.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/equipment-type/gasoline-fleets-oil-change-service-centers/truck-fleets</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:05:35.736Z</t>
+  </si>
+  <si>
+    <t>Products for Truck Fleets: Lubricants, Coolants &amp; More | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/gasoline_fleets_oil_change_service_centers/truck_fleets.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/cement-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/cement-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:05:42.960Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils: Cement Mixers &amp; Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/cement_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/circulating-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/circulating-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:05:49.903Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils: Circulating Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/circulating_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/compressors.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/compressors</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:05:56.002Z</t>
+  </si>
+  <si>
+    <t>Industrial Compressor Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/compressors.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/conveyors.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/conveyors</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:03.048Z</t>
+  </si>
+  <si>
+    <t>Industrial Conveyor Lubricants &amp; Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/conveyors.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/injection-molding-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/injection-molding-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:09.535Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils: Injection Molding Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/injection_molding_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/lifts.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/lifts</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:16.635Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Lifts | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/lifts.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/manufacturing-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/manufacturing-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:24.602Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils: Manufacturing Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/manufacturing_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/mining-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/mining-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:32.163Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Mining Equipment | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/mining_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/oil-gas-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/oil-gas-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:39.294Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Oil &amp; Gas Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/oil_gas_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/paper-machines.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/paper-machines</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:46.182Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Paper Machines | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/paper_machines.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/power-generation-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/power-generation-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:06:53.070Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Power Generation Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/power_generation_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/steel-mills.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/industrial-equipment-machinery/steel-mills</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:01.501Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Steel Mills  | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/industrial_equipment_machinery/steel_mills.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/agriculture-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/agriculture-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:09.404Z</t>
+  </si>
+  <si>
+    <t>Agriculture Equipment Lubricants: Greases, Oils &amp; More | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/off_highway_heavy_duty/agriculture_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/construction-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/construction-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:16.559Z</t>
+  </si>
+  <si>
+    <t>Construction Equipment Lubricants: Greases, Oils, &amp; More | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/off_highway_heavy_duty/construction_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/forestry-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/forestry-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:25.104Z</t>
+  </si>
+  <si>
+    <t>Forestry Equipment Lubricants: Greases, Fluids, Oils &amp; More | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/off_highway_heavy_duty/forestry_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/inland-marine-equipment.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/inland-marine-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:33.737Z</t>
+  </si>
+  <si>
+    <t>Lubricants for Inland Marine Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/off_highway_heavy_duty/inland_marine_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/mining-equipment.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/off-highway-heavy-duty/mining-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:41.842Z</t>
+  </si>
+  <si>
+    <t>Mining Equipment Lubricants: Greases, Oils &amp; More | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/off_highway_heavy_duty/mining_equipment.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/buses.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/buses</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:48.282Z</t>
+  </si>
+  <si>
+    <t>Engine Oils &amp; Coolants for Buses | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/on_highway_heavy_duty/buses.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/light-duty-and-diesel-pick-up-trucks.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/light-duty-and-diesel-pick-up-trucks</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:07:56.735Z</t>
+  </si>
+  <si>
+    <t>Engine Oils: Light Duty &amp; Diesel Pickup Trucks | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/on_highway_heavy_duty/light_duty_and_diesel_pick_up_trucks.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/medium-large-trucks.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/medium-large-trucks</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:08:05.762Z</t>
+  </si>
+  <si>
+    <t>Engine Oils: Medium &amp; Large Trucks | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/on_highway_heavy_duty/medium_large_trucks.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/waste-hauler.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/on-highway-heavy-duty/waste-hauler</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:08:13.752Z</t>
+  </si>
+  <si>
+    <t>Engine Oils &amp; Coolants for Waste Haulers | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/on_highway_heavy_duty/waste_hauler.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/atvs-utvs-snowmobiles.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/atvs-utvs-snowmobiles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:08:20.548Z</t>
+  </si>
+  <si>
+    <t>Engine Oils: ATVs, UTVs &amp; Snowmobiles | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/atvs_utvs_snowmobiles.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/boats.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/boats</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:08:27.116Z</t>
+  </si>
+  <si>
+    <t>Engine Oils &amp; Coolants for Boats | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/boats.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/cars-suvs.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/cars-suvs</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:15:54.544Z</t>
+  </si>
+  <si>
+    <t>Motor Oils &amp; Coolants for Your Car or SUV | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/cars_suvs.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/motorcycles.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/motorcycles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:08:40.977Z</t>
+  </si>
+  <si>
+    <t>Motorcycle Engine Oils &amp; Coolants | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/motorcycles.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/pick-up-trucks-sprinter-vans-diesel.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/pick-up-trucks-sprinter-vans-diesel</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:08:48.914Z</t>
+  </si>
+  <si>
+    <t>Motor Oils for Diesel Pickup Trucks &amp; Vans | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/pick_up_trucks_sprinter_vans_diesel.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/pick-up-trucks-sprinter-vans-gasoline.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/pick-up-trucks-sprinter-vans-gasoline</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:16:01.573Z</t>
+  </si>
+  <si>
+    <t>Motor Oils for Gasoline Pickup Trucks &amp; Vans | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/pick_up_trucks_sprinter_vans_gasoline.html</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/professional-lawn-care.report.json</t>
+  </si>
+  <si>
+    <t>products/equipment-type/personal-rec-vehicles/professional-lawn-care</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:02.461Z</t>
+  </si>
+  <si>
+    <t>Lawn Mower Engine Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/equipment_type/personal_rec_vehicles/professional_lawn_care.html</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/gasoline-fleets.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/gasoline-fleets</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:09.761Z</t>
+  </si>
+  <si>
+    <t>Gasoline Fleet Coolants &amp; Antifreezes | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/coolants_antifreezes/gasoline_fleets.html</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/industrial.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/industrial</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:18.461Z</t>
+  </si>
+  <si>
+    <t>Industrial Equipment Coolants &amp; Antifreezes | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/coolants_antifreezes/industrial.html</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/off-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/off-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:24.516Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Coolants &amp; Antifreezes: Off Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/coolants_antifreezes/off_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/on-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/on-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:32.023Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Coolants &amp; Antifreezes: On Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/coolants_antifreezes/on_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/personal-rec-vehicles.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/coolants-antifreezes/personal-rec-vehicles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:37.613Z</t>
+  </si>
+  <si>
+    <t>Coolants &amp; Antifreezes for Your Car | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/coolants_antifreezes/personal_rec_vehicles.html</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/gasoline-fleets.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/gasoline-fleets</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:44.983Z</t>
+  </si>
+  <si>
+    <t>Engine Oils for Gasoline Fleets | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/engine_oils/gasoline_fleets.html</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/industrial.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/industrial</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:09:52.701Z</t>
+  </si>
+  <si>
+    <t>Industrial Machinery Engine Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/engine_oils/industrial.html</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/off-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>["cards-products","cards-products","cards-products","cards-products"]</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/off-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:00.801Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Engine Oils: Off Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/engine_oils/off_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/on-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/on-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:09.444Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Engine Oils: On Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/engine_oils/on_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/personal-rec-vehicles.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/engine-oils/personal-rec-vehicles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:16.252Z</t>
+  </si>
+  <si>
+    <t>Motor Oil &amp; Synthetic Motor Oil for Cars | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/engine_oils/personal_rec_vehicles.html</t>
+  </si>
+  <si>
+    <t>products/product-category/fuel-additives/personal-rec-vehicles.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/fuel-additives/personal-rec-vehicles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:22.338Z</t>
+  </si>
+  <si>
+    <t>Car Fuel System &amp; Fuel Injector Cleaners | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/fuel_additives/personal_rec_vehicles.html</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/gasoline-fleets.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/gasoline-fleets</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:28.285Z</t>
+  </si>
+  <si>
+    <t>Greases for Gasoline Fleets | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/greases/gasoline_fleets.html</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/industrial.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/industrial</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:35.922Z</t>
+  </si>
+  <si>
+    <t>Industrial Greases | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/greases/industrial.html</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/off-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/off-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:42.856Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Greases: Off Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/greases/off_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/on-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/on-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:49.933Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Greases: On Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/greases/on_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/personal-rec-vehicles.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/greases/personal-rec-vehicles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:10:56.425Z</t>
+  </si>
+  <si>
+    <t>Greases for Cars, Trucks &amp; SUVs | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/greases/personal_rec_vehicles.html</t>
+  </si>
+  <si>
+    <t>products/product-category/hydraulic-oils/industrial.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/hydraulic-oils/industrial</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:04.986Z</t>
+  </si>
+  <si>
+    <t>Hydraulic Oils for Industrial Machinery | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/hydraulic_oils/industrial.html</t>
+  </si>
+  <si>
+    <t>products/product-category/hydraulic-oils/off-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/hydraulic-oils/off-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:13.939Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Hydraulic Oils: Off Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/hydraulic_oils/off_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/hydraulic-oils/on-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/hydraulic-oils/on-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:20.001Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Hydraulic Oils: On Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/hydraulic_oils/on_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/circulating-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/circulating-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:27.454Z</t>
+  </si>
+  <si>
+    <t>Circulating Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/circulating_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/compressor-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/compressor-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:33.573Z</t>
+  </si>
+  <si>
+    <t>Compressor Oils, Air Compressor Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/compressor_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/gear-box-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/gear-box-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:40.604Z</t>
+  </si>
+  <si>
+    <t>Industrial Gear Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/gear_box_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/hydraulic-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/hydraulic-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:48.114Z</t>
+  </si>
+  <si>
+    <t>Hydraulic Oils &amp; Hydraulic Fluids | Chevron Lubricants (US) | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/hydraulic_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/metal-working-equipment-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/metal-working-equipment-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:11:54.206Z</t>
+  </si>
+  <si>
+    <t>Industrial Metalworking Oils &amp; Fluids | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/metal_working_equipment_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/mining-equipment-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/mining-equipment-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:01.360Z</t>
+  </si>
+  <si>
+    <t>Mining Equipment Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/mining_equipment_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/paper-machine-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/paper-machine-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:09.304Z</t>
+  </si>
+  <si>
+    <t>Paper Machine Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/paper_machine_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/specialty-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/specialty-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:16.932Z</t>
+  </si>
+  <si>
+    <t>Industrial Oils for Specialty Equipment | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/specialty_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/turbine-oils.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/industrial-oils/turbine-oils</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:23.600Z</t>
+  </si>
+  <si>
+    <t>Turbine Oils | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/industrial_oils/turbine_oils.html</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/gasoline-fleets.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/gasoline-fleets</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:16:10.147Z</t>
+  </si>
+  <si>
+    <t>Gear Oils &amp; Transmission Fluids: Gas Fleets | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/transmission_gear_oils/gasoline_fleets.html</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/industrial.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/industrial</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:36.551Z</t>
+  </si>
+  <si>
+    <t>Industrial Gear Oils &amp; Transmission Fluids | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/transmission_gear_oils/industrial.html</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/off-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/off-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:43.540Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Gear Oils: Off Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/transmission_gear_oils/off_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/on-highway-heavy-duty.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/on-highway-heavy-duty</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:12:52.001Z</t>
+  </si>
+  <si>
+    <t>Heavy Duty Gear Oils: On Highway | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/transmission_gear_oils/on_highway_heavy_duty.html</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/personal-rec-vehicles.report.json</t>
+  </si>
+  <si>
+    <t>products/product-category/transmission-gear-oils/personal-rec-vehicles</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:16:18.100Z</t>
+  </si>
+  <si>
+    <t>Gear Oils &amp; Transmission Fluids for your Car | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/products/product_category/transmission_gear_oils/personal_rec_vehicles.html</t>
+  </si>
+  <si>
+    <t>services/pro-services/personal-rec-vehicles/xpress-lube-contact-us.report.json</t>
+  </si>
+  <si>
+    <t>services/pro-services/personal-rec-vehicles/xpress-lube-contact-us</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:04:25.603Z</t>
+  </si>
+  <si>
+    <t>xpress lube contact us | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/services/pro-services/personal-rec-vehicles/xpress-lube-contact-us.html</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/emissions-control-center/on-hwy-the-solution.report.json</t>
+  </si>
+  <si>
+    <t>["hero-overlay"]</t>
+  </si>
+  <si>
+    <t>learning/about-our-brands/delo/emissions-control-center/on-hwy-the-solution</t>
+  </si>
+  <si>
+    <t>2026-10-30T03:00:36.132Z</t>
+  </si>
+  <si>
+    <t>DPF Low Ash Oil | Delo Emissions Control Center, On Hwy | Chevron Lubricants (US)</t>
+  </si>
+  <si>
+    <t>https://www.chevronlubricants.com/en_us/home/learning/about-our-brands/delo/emissions-control-center/on-hwy-the-solution.html</t>
   </si>
 </sst>
 </file>
@@ -456,16 +2259,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -525,25 +2325,2911 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" t="s">
+        <v>156</v>
+      </c>
+      <c r="G27" t="s">
+        <v>157</v>
+      </c>
+      <c r="H27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" t="s">
+        <v>163</v>
+      </c>
+      <c r="H28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" t="s">
+        <v>168</v>
+      </c>
+      <c r="G29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" t="s">
+        <v>179</v>
+      </c>
+      <c r="G31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>191</v>
+      </c>
+      <c r="G33" t="s">
+        <v>192</v>
+      </c>
+      <c r="H33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" t="s">
+        <v>197</v>
+      </c>
+      <c r="G34" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" t="s">
+        <v>204</v>
+      </c>
+      <c r="H35" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" t="s">
+        <v>209</v>
+      </c>
+      <c r="G36" t="s">
+        <v>210</v>
+      </c>
+      <c r="H36" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s">
+        <v>215</v>
+      </c>
+      <c r="G37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" t="s">
+        <v>219</v>
+      </c>
+      <c r="C38" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="s">
+        <v>221</v>
+      </c>
+      <c r="G38" t="s">
+        <v>222</v>
+      </c>
+      <c r="H38" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" t="s">
+        <v>225</v>
+      </c>
+      <c r="C39" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" t="s">
+        <v>227</v>
+      </c>
+      <c r="G39" t="s">
+        <v>228</v>
+      </c>
+      <c r="H39" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>233</v>
+      </c>
+      <c r="G40" t="s">
+        <v>234</v>
+      </c>
+      <c r="H40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" t="s">
+        <v>237</v>
+      </c>
+      <c r="C41" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" t="s">
+        <v>240</v>
+      </c>
+      <c r="H41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" t="s">
+        <v>245</v>
+      </c>
+      <c r="G42" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>248</v>
+      </c>
+      <c r="B43" t="s">
+        <v>249</v>
+      </c>
+      <c r="C43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>251</v>
+      </c>
+      <c r="G43" t="s">
+        <v>252</v>
+      </c>
+      <c r="H43" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>254</v>
+      </c>
+      <c r="B44" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" t="s">
+        <v>256</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="s">
+        <v>257</v>
+      </c>
+      <c r="G44" t="s">
+        <v>258</v>
+      </c>
+      <c r="H44" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>260</v>
+      </c>
+      <c r="B45" t="s">
+        <v>261</v>
+      </c>
+      <c r="C45" t="s">
+        <v>262</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" t="s">
+        <v>263</v>
+      </c>
+      <c r="G45" t="s">
+        <v>264</v>
+      </c>
+      <c r="H45" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>266</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>267</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" t="s">
+        <v>268</v>
+      </c>
+      <c r="G46" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>270</v>
+      </c>
+      <c r="B47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" t="s">
+        <v>273</v>
+      </c>
+      <c r="G47" t="s">
+        <v>274</v>
+      </c>
+      <c r="H47" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>276</v>
+      </c>
+      <c r="B48" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" t="s">
+        <v>277</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" t="s">
+        <v>278</v>
+      </c>
+      <c r="G48" t="s">
+        <v>279</v>
+      </c>
+      <c r="H48" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>281</v>
+      </c>
+      <c r="B49" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" t="s">
+        <v>282</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>283</v>
+      </c>
+      <c r="F49" t="s">
+        <v>284</v>
+      </c>
+      <c r="G49" t="s">
+        <v>285</v>
+      </c>
+      <c r="H49" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>287</v>
+      </c>
+      <c r="B50" t="s">
+        <v>288</v>
+      </c>
+      <c r="C50" t="s">
+        <v>289</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>283</v>
+      </c>
+      <c r="F50" t="s">
+        <v>290</v>
+      </c>
+      <c r="G50" t="s">
+        <v>291</v>
+      </c>
+      <c r="H50" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>293</v>
+      </c>
+      <c r="B51" t="s">
+        <v>294</v>
+      </c>
+      <c r="C51" t="s">
+        <v>295</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>283</v>
+      </c>
+      <c r="F51" t="s">
+        <v>296</v>
+      </c>
+      <c r="G51" t="s">
+        <v>297</v>
+      </c>
+      <c r="H51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>299</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>300</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>283</v>
+      </c>
+      <c r="F52" t="s">
+        <v>301</v>
+      </c>
+      <c r="G52" t="s">
+        <v>302</v>
+      </c>
+      <c r="H52" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>304</v>
+      </c>
+      <c r="B53" t="s">
+        <v>288</v>
+      </c>
+      <c r="C53" t="s">
+        <v>305</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F53" t="s">
+        <v>306</v>
+      </c>
+      <c r="G53" t="s">
+        <v>307</v>
+      </c>
+      <c r="H53" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>309</v>
+      </c>
+      <c r="B54" t="s">
+        <v>294</v>
+      </c>
+      <c r="C54" t="s">
+        <v>310</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>283</v>
+      </c>
+      <c r="F54" t="s">
+        <v>311</v>
+      </c>
+      <c r="G54" t="s">
+        <v>312</v>
+      </c>
+      <c r="H54" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>314</v>
+      </c>
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" t="s">
+        <v>315</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>283</v>
+      </c>
+      <c r="F55" t="s">
+        <v>316</v>
+      </c>
+      <c r="G55" t="s">
+        <v>317</v>
+      </c>
+      <c r="H55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>319</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" t="s">
+        <v>320</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>283</v>
+      </c>
+      <c r="F56" t="s">
+        <v>321</v>
+      </c>
+      <c r="G56" t="s">
+        <v>322</v>
+      </c>
+      <c r="H56" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>324</v>
+      </c>
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s">
+        <v>325</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>283</v>
+      </c>
+      <c r="F57" t="s">
+        <v>326</v>
+      </c>
+      <c r="G57" t="s">
+        <v>327</v>
+      </c>
+      <c r="H57" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>329</v>
+      </c>
+      <c r="B58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" t="s">
+        <v>330</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>283</v>
+      </c>
+      <c r="F58" t="s">
+        <v>331</v>
+      </c>
+      <c r="G58" t="s">
+        <v>332</v>
+      </c>
+      <c r="H58" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>334</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>283</v>
+      </c>
+      <c r="F59" t="s">
+        <v>336</v>
+      </c>
+      <c r="G59" t="s">
+        <v>337</v>
+      </c>
+      <c r="H59" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>339</v>
+      </c>
+      <c r="B60" t="s">
+        <v>294</v>
+      </c>
+      <c r="C60" t="s">
+        <v>340</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>283</v>
+      </c>
+      <c r="F60" t="s">
+        <v>341</v>
+      </c>
+      <c r="G60" t="s">
+        <v>342</v>
+      </c>
+      <c r="H60" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>344</v>
+      </c>
+      <c r="B61" t="s">
+        <v>288</v>
+      </c>
+      <c r="C61" t="s">
+        <v>345</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>283</v>
+      </c>
+      <c r="F61" t="s">
+        <v>346</v>
+      </c>
+      <c r="G61" t="s">
+        <v>347</v>
+      </c>
+      <c r="H61" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>349</v>
+      </c>
+      <c r="B62" t="s">
+        <v>288</v>
+      </c>
+      <c r="C62" t="s">
+        <v>350</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>283</v>
+      </c>
+      <c r="F62" t="s">
+        <v>351</v>
+      </c>
+      <c r="G62" t="s">
+        <v>352</v>
+      </c>
+      <c r="H62" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>354</v>
+      </c>
+      <c r="B63" t="s">
+        <v>288</v>
+      </c>
+      <c r="C63" t="s">
+        <v>355</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>283</v>
+      </c>
+      <c r="F63" t="s">
+        <v>356</v>
+      </c>
+      <c r="G63" t="s">
+        <v>357</v>
+      </c>
+      <c r="H63" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>359</v>
+      </c>
+      <c r="B64" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" t="s">
+        <v>360</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>283</v>
+      </c>
+      <c r="F64" t="s">
+        <v>361</v>
+      </c>
+      <c r="G64" t="s">
+        <v>362</v>
+      </c>
+      <c r="H64" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>364</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>365</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>283</v>
+      </c>
+      <c r="F65" t="s">
+        <v>366</v>
+      </c>
+      <c r="G65" t="s">
+        <v>367</v>
+      </c>
+      <c r="H65" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>369</v>
+      </c>
+      <c r="B66" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" t="s">
+        <v>370</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>283</v>
+      </c>
+      <c r="F66" t="s">
+        <v>371</v>
+      </c>
+      <c r="G66" t="s">
+        <v>372</v>
+      </c>
+      <c r="H66" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>374</v>
+      </c>
+      <c r="B67" t="s">
+        <v>375</v>
+      </c>
+      <c r="C67" t="s">
+        <v>376</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>283</v>
+      </c>
+      <c r="F67" t="s">
+        <v>377</v>
+      </c>
+      <c r="G67" t="s">
+        <v>378</v>
+      </c>
+      <c r="H67" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>380</v>
+      </c>
+      <c r="B68" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" t="s">
+        <v>381</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>283</v>
+      </c>
+      <c r="F68" t="s">
+        <v>382</v>
+      </c>
+      <c r="G68" t="s">
+        <v>383</v>
+      </c>
+      <c r="H68" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>385</v>
+      </c>
+      <c r="B69" t="s">
+        <v>107</v>
+      </c>
+      <c r="C69" t="s">
+        <v>386</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>283</v>
+      </c>
+      <c r="F69" t="s">
+        <v>387</v>
+      </c>
+      <c r="G69" t="s">
+        <v>388</v>
+      </c>
+      <c r="H69" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>390</v>
+      </c>
+      <c r="B70" t="s">
+        <v>391</v>
+      </c>
+      <c r="C70" t="s">
+        <v>392</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" t="s">
+        <v>393</v>
+      </c>
+      <c r="G70" t="s">
+        <v>394</v>
+      </c>
+      <c r="H70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>396</v>
+      </c>
+      <c r="B71" t="s">
+        <v>294</v>
+      </c>
+      <c r="C71" t="s">
+        <v>397</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>283</v>
+      </c>
+      <c r="F71" t="s">
+        <v>398</v>
+      </c>
+      <c r="G71" t="s">
+        <v>399</v>
+      </c>
+      <c r="H71" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>401</v>
+      </c>
+      <c r="B72" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" t="s">
+        <v>402</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>283</v>
+      </c>
+      <c r="F72" t="s">
+        <v>403</v>
+      </c>
+      <c r="G72" t="s">
+        <v>404</v>
+      </c>
+      <c r="H72" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>406</v>
+      </c>
+      <c r="B73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" t="s">
+        <v>407</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>283</v>
+      </c>
+      <c r="F73" t="s">
+        <v>408</v>
+      </c>
+      <c r="G73" t="s">
+        <v>409</v>
+      </c>
+      <c r="H73" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>411</v>
+      </c>
+      <c r="B74" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" t="s">
+        <v>412</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>283</v>
+      </c>
+      <c r="F74" t="s">
+        <v>413</v>
+      </c>
+      <c r="G74" t="s">
+        <v>414</v>
+      </c>
+      <c r="H74" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>416</v>
+      </c>
+      <c r="B75" t="s">
+        <v>107</v>
+      </c>
+      <c r="C75" t="s">
+        <v>417</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>283</v>
+      </c>
+      <c r="F75" t="s">
+        <v>418</v>
+      </c>
+      <c r="G75" t="s">
+        <v>419</v>
+      </c>
+      <c r="H75" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>421</v>
+      </c>
+      <c r="B76" t="s">
+        <v>113</v>
+      </c>
+      <c r="C76" t="s">
+        <v>422</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>283</v>
+      </c>
+      <c r="F76" t="s">
+        <v>423</v>
+      </c>
+      <c r="G76" t="s">
+        <v>424</v>
+      </c>
+      <c r="H76" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>426</v>
+      </c>
+      <c r="B77" t="s">
+        <v>288</v>
+      </c>
+      <c r="C77" t="s">
+        <v>427</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>283</v>
+      </c>
+      <c r="F77" t="s">
+        <v>428</v>
+      </c>
+      <c r="G77" t="s">
+        <v>429</v>
+      </c>
+      <c r="H77" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>431</v>
+      </c>
+      <c r="B78" t="s">
+        <v>288</v>
+      </c>
+      <c r="C78" t="s">
+        <v>432</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>283</v>
+      </c>
+      <c r="F78" t="s">
+        <v>433</v>
+      </c>
+      <c r="G78" t="s">
+        <v>434</v>
+      </c>
+      <c r="H78" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>436</v>
+      </c>
+      <c r="B79" t="s">
+        <v>113</v>
+      </c>
+      <c r="C79" t="s">
+        <v>437</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>283</v>
+      </c>
+      <c r="F79" t="s">
+        <v>438</v>
+      </c>
+      <c r="G79" t="s">
+        <v>439</v>
+      </c>
+      <c r="H79" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>441</v>
+      </c>
+      <c r="B80" t="s">
+        <v>113</v>
+      </c>
+      <c r="C80" t="s">
+        <v>442</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F80" t="s">
+        <v>443</v>
+      </c>
+      <c r="G80" t="s">
+        <v>444</v>
+      </c>
+      <c r="H80" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>446</v>
+      </c>
+      <c r="B81" t="s">
+        <v>447</v>
+      </c>
+      <c r="C81" t="s">
+        <v>448</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>283</v>
+      </c>
+      <c r="F81" t="s">
+        <v>449</v>
+      </c>
+      <c r="G81" t="s">
+        <v>450</v>
+      </c>
+      <c r="H81" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>452</v>
+      </c>
+      <c r="B82" t="s">
+        <v>447</v>
+      </c>
+      <c r="C82" t="s">
+        <v>453</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>283</v>
+      </c>
+      <c r="F82" t="s">
+        <v>454</v>
+      </c>
+      <c r="G82" t="s">
+        <v>455</v>
+      </c>
+      <c r="H82" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>457</v>
+      </c>
+      <c r="B83" t="s">
+        <v>447</v>
+      </c>
+      <c r="C83" t="s">
+        <v>458</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>283</v>
+      </c>
+      <c r="F83" t="s">
+        <v>459</v>
+      </c>
+      <c r="G83" t="s">
+        <v>460</v>
+      </c>
+      <c r="H83" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>462</v>
+      </c>
+      <c r="B84" t="s">
+        <v>113</v>
+      </c>
+      <c r="C84" t="s">
+        <v>463</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>283</v>
+      </c>
+      <c r="F84" t="s">
+        <v>464</v>
+      </c>
+      <c r="G84" t="s">
+        <v>465</v>
+      </c>
+      <c r="H84" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>467</v>
+      </c>
+      <c r="B85" t="s">
+        <v>468</v>
+      </c>
+      <c r="C85" t="s">
+        <v>469</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>283</v>
+      </c>
+      <c r="F85" t="s">
+        <v>470</v>
+      </c>
+      <c r="G85" t="s">
+        <v>471</v>
+      </c>
+      <c r="H85" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>473</v>
+      </c>
+      <c r="B86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" t="s">
+        <v>474</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>283</v>
+      </c>
+      <c r="F86" t="s">
+        <v>475</v>
+      </c>
+      <c r="G86" t="s">
+        <v>476</v>
+      </c>
+      <c r="H86" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>478</v>
+      </c>
+      <c r="B87" t="s">
+        <v>479</v>
+      </c>
+      <c r="C87" t="s">
+        <v>480</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>283</v>
+      </c>
+      <c r="F87" t="s">
+        <v>481</v>
+      </c>
+      <c r="G87" t="s">
+        <v>482</v>
+      </c>
+      <c r="H87" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>484</v>
+      </c>
+      <c r="B88" t="s">
+        <v>479</v>
+      </c>
+      <c r="C88" t="s">
+        <v>485</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>283</v>
+      </c>
+      <c r="F88" t="s">
+        <v>486</v>
+      </c>
+      <c r="G88" t="s">
+        <v>487</v>
+      </c>
+      <c r="H88" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>489</v>
+      </c>
+      <c r="B89" t="s">
+        <v>447</v>
+      </c>
+      <c r="C89" t="s">
+        <v>490</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" t="s">
+        <v>283</v>
+      </c>
+      <c r="F89" t="s">
+        <v>491</v>
+      </c>
+      <c r="G89" t="s">
+        <v>492</v>
+      </c>
+      <c r="H89" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>494</v>
+      </c>
+      <c r="B90" t="s">
+        <v>113</v>
+      </c>
+      <c r="C90" t="s">
+        <v>495</v>
+      </c>
+      <c r="D90" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" t="s">
+        <v>283</v>
+      </c>
+      <c r="F90" t="s">
+        <v>496</v>
+      </c>
+      <c r="G90" t="s">
+        <v>497</v>
+      </c>
+      <c r="H90" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>499</v>
+      </c>
+      <c r="B91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" t="s">
+        <v>500</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" t="s">
+        <v>283</v>
+      </c>
+      <c r="F91" t="s">
+        <v>501</v>
+      </c>
+      <c r="G91" t="s">
+        <v>502</v>
+      </c>
+      <c r="H91" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>504</v>
+      </c>
+      <c r="B92" t="s">
+        <v>447</v>
+      </c>
+      <c r="C92" t="s">
+        <v>505</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" t="s">
+        <v>283</v>
+      </c>
+      <c r="F92" t="s">
+        <v>506</v>
+      </c>
+      <c r="G92" t="s">
+        <v>507</v>
+      </c>
+      <c r="H92" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>509</v>
+      </c>
+      <c r="B93" t="s">
+        <v>468</v>
+      </c>
+      <c r="C93" t="s">
+        <v>510</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>283</v>
+      </c>
+      <c r="F93" t="s">
+        <v>511</v>
+      </c>
+      <c r="G93" t="s">
+        <v>512</v>
+      </c>
+      <c r="H93" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>514</v>
+      </c>
+      <c r="B94" t="s">
+        <v>447</v>
+      </c>
+      <c r="C94" t="s">
+        <v>515</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>283</v>
+      </c>
+      <c r="F94" t="s">
+        <v>516</v>
+      </c>
+      <c r="G94" t="s">
+        <v>517</v>
+      </c>
+      <c r="H94" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>519</v>
+      </c>
+      <c r="B95" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" t="s">
+        <v>520</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" t="s">
+        <v>283</v>
+      </c>
+      <c r="F95" t="s">
+        <v>521</v>
+      </c>
+      <c r="G95" t="s">
+        <v>522</v>
+      </c>
+      <c r="H95" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>524</v>
+      </c>
+      <c r="B96" t="s">
+        <v>447</v>
+      </c>
+      <c r="C96" t="s">
+        <v>525</v>
+      </c>
+      <c r="D96" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" t="s">
+        <v>283</v>
+      </c>
+      <c r="F96" t="s">
+        <v>526</v>
+      </c>
+      <c r="G96" t="s">
+        <v>527</v>
+      </c>
+      <c r="H96" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>529</v>
+      </c>
+      <c r="B97" t="s">
+        <v>113</v>
+      </c>
+      <c r="C97" t="s">
+        <v>530</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s">
+        <v>283</v>
+      </c>
+      <c r="F97" t="s">
+        <v>531</v>
+      </c>
+      <c r="G97" t="s">
+        <v>532</v>
+      </c>
+      <c r="H97" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>534</v>
+      </c>
+      <c r="B98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C98" t="s">
+        <v>535</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s">
+        <v>283</v>
+      </c>
+      <c r="F98" t="s">
+        <v>536</v>
+      </c>
+      <c r="G98" t="s">
+        <v>537</v>
+      </c>
+      <c r="H98" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>539</v>
+      </c>
+      <c r="B99" t="s">
+        <v>96</v>
+      </c>
+      <c r="C99" t="s">
+        <v>540</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>283</v>
+      </c>
+      <c r="F99" t="s">
+        <v>541</v>
+      </c>
+      <c r="G99" t="s">
+        <v>542</v>
+      </c>
+      <c r="H99" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>544</v>
+      </c>
+      <c r="B100" t="s">
+        <v>468</v>
+      </c>
+      <c r="C100" t="s">
+        <v>545</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>283</v>
+      </c>
+      <c r="F100" t="s">
+        <v>546</v>
+      </c>
+      <c r="G100" t="s">
+        <v>547</v>
+      </c>
+      <c r="H100" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>549</v>
+      </c>
+      <c r="B101" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" t="s">
+        <v>550</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" t="s">
+        <v>283</v>
+      </c>
+      <c r="F101" t="s">
+        <v>551</v>
+      </c>
+      <c r="G101" t="s">
+        <v>552</v>
+      </c>
+      <c r="H101" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>554</v>
+      </c>
+      <c r="B102" t="s">
+        <v>479</v>
+      </c>
+      <c r="C102" t="s">
+        <v>555</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>283</v>
+      </c>
+      <c r="F102" t="s">
+        <v>556</v>
+      </c>
+      <c r="G102" t="s">
+        <v>557</v>
+      </c>
+      <c r="H102" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>559</v>
+      </c>
+      <c r="B103" t="s">
+        <v>468</v>
+      </c>
+      <c r="C103" t="s">
+        <v>560</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s">
+        <v>283</v>
+      </c>
+      <c r="F103" t="s">
+        <v>561</v>
+      </c>
+      <c r="G103" t="s">
+        <v>562</v>
+      </c>
+      <c r="H103" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>564</v>
+      </c>
+      <c r="B104" t="s">
+        <v>96</v>
+      </c>
+      <c r="C104" t="s">
+        <v>565</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s">
+        <v>283</v>
+      </c>
+      <c r="F104" t="s">
+        <v>566</v>
+      </c>
+      <c r="G104" t="s">
+        <v>567</v>
+      </c>
+      <c r="H104" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>569</v>
+      </c>
+      <c r="B105" t="s">
+        <v>479</v>
+      </c>
+      <c r="C105" t="s">
+        <v>570</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>283</v>
+      </c>
+      <c r="F105" t="s">
+        <v>571</v>
+      </c>
+      <c r="G105" t="s">
+        <v>572</v>
+      </c>
+      <c r="H105" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>574</v>
+      </c>
+      <c r="B106" t="s">
+        <v>113</v>
+      </c>
+      <c r="C106" t="s">
+        <v>575</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>283</v>
+      </c>
+      <c r="F106" t="s">
+        <v>576</v>
+      </c>
+      <c r="G106" t="s">
+        <v>577</v>
+      </c>
+      <c r="H106" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>579</v>
+      </c>
+      <c r="B107" t="s">
+        <v>479</v>
+      </c>
+      <c r="C107" t="s">
+        <v>580</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" t="s">
+        <v>283</v>
+      </c>
+      <c r="F107" t="s">
+        <v>581</v>
+      </c>
+      <c r="G107" t="s">
+        <v>582</v>
+      </c>
+      <c r="H107" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>584</v>
+      </c>
+      <c r="B108" t="s">
+        <v>447</v>
+      </c>
+      <c r="C108" t="s">
+        <v>585</v>
+      </c>
+      <c r="D108" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" t="s">
+        <v>283</v>
+      </c>
+      <c r="F108" t="s">
+        <v>586</v>
+      </c>
+      <c r="G108" t="s">
+        <v>587</v>
+      </c>
+      <c r="H108" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>589</v>
+      </c>
+      <c r="B109" t="s">
+        <v>447</v>
+      </c>
+      <c r="C109" t="s">
+        <v>590</v>
+      </c>
+      <c r="D109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" t="s">
+        <v>283</v>
+      </c>
+      <c r="F109" t="s">
+        <v>591</v>
+      </c>
+      <c r="G109" t="s">
+        <v>592</v>
+      </c>
+      <c r="H109" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>594</v>
+      </c>
+      <c r="B110" t="s">
+        <v>468</v>
+      </c>
+      <c r="C110" t="s">
+        <v>595</v>
+      </c>
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" t="s">
+        <v>283</v>
+      </c>
+      <c r="F110" t="s">
+        <v>596</v>
+      </c>
+      <c r="G110" t="s">
+        <v>597</v>
+      </c>
+      <c r="H110" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>599</v>
+      </c>
+      <c r="B111" t="s">
+        <v>468</v>
+      </c>
+      <c r="C111" t="s">
+        <v>600</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s">
+        <v>283</v>
+      </c>
+      <c r="F111" t="s">
+        <v>601</v>
+      </c>
+      <c r="G111" t="s">
+        <v>602</v>
+      </c>
+      <c r="H111" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>604</v>
+      </c>
+      <c r="B112" t="s">
+        <v>447</v>
+      </c>
+      <c r="C112" t="s">
+        <v>605</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
+        <v>283</v>
+      </c>
+      <c r="F112" t="s">
+        <v>606</v>
+      </c>
+      <c r="G112" t="s">
+        <v>607</v>
+      </c>
+      <c r="H112" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>609</v>
+      </c>
+      <c r="B113" t="s">
+        <v>136</v>
+      </c>
+      <c r="C113" t="s">
+        <v>610</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" t="s">
+        <v>49</v>
+      </c>
+      <c r="F113" t="s">
+        <v>611</v>
+      </c>
+      <c r="G113" t="s">
+        <v>612</v>
+      </c>
+      <c r="H113" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>614</v>
+      </c>
+      <c r="B114" t="s">
+        <v>615</v>
+      </c>
+      <c r="C114" t="s">
+        <v>616</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>49</v>
+      </c>
+      <c r="F114" t="s">
+        <v>617</v>
+      </c>
+      <c r="G114" t="s">
+        <v>618</v>
+      </c>
+      <c r="H114" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>
